--- a/excel-files/MANILA/I. VILLAMOR HIGH SCHOOL.xlsx
+++ b/excel-files/MANILA/I. VILLAMOR HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC860AB-1713-4660-97DC-C056805343EF}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0665E96-552D-45A4-A209-95867F231947}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5410,11 +5410,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E98" xr:uid="{B95953FD-0030-421C-AD35-CA802FF838F6}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5651,7 +5651,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9322,7 +9322,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="12"/>
-      <c r="F63" s="10"/>
+      <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="12"/>
-      <c r="F64" s="10"/>
+      <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
@@ -9460,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="12"/>
-      <c r="F65" s="10"/>
+      <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="12"/>
-      <c r="F66" s="10"/>
+      <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="12"/>
-      <c r="F67" s="10"/>
+      <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="12"/>
-      <c r="F68" s="10"/>
+      <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
@@ -9736,7 +9736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="12"/>
-      <c r="F69" s="10"/>
+      <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="12"/>
-      <c r="F70" s="10"/>
+      <c r="F70" s="12"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
@@ -9874,7 +9874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="12"/>
-      <c r="F71" s="10"/>
+      <c r="F71" s="12"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
@@ -9943,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9957,7 +9957,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="12"/>
-      <c r="F73" s="10"/>
+      <c r="F73" s="12"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
@@ -10026,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="12"/>
-      <c r="F74" s="10"/>
+      <c r="F74" s="12"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
@@ -10095,7 +10095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="12"/>
-      <c r="F75" s="10"/>
+      <c r="F75" s="12"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
@@ -10164,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="12"/>
-      <c r="F76" s="10"/>
+      <c r="F76" s="12"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
@@ -10233,7 +10233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="12"/>
-      <c r="F77" s="10"/>
+      <c r="F77" s="12"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12">
         <f t="shared" si="2"/>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="12"/>
-      <c r="F78" s="10"/>
+      <c r="F78" s="12"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
@@ -10371,7 +10371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="12"/>
-      <c r="F79" s="10"/>
+      <c r="F79" s="12"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
         <f t="shared" si="22"/>
@@ -10440,7 +10440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="12"/>
-      <c r="F80" s="10"/>
+      <c r="F80" s="12"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
         <f t="shared" si="22"/>
@@ -10509,7 +10509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="12"/>
-      <c r="F81" s="10"/>
+      <c r="F81" s="12"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
         <f t="shared" si="22"/>
@@ -10578,7 +10578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10592,7 +10592,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="12"/>
-      <c r="F83" s="10"/>
+      <c r="F83" s="12"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
         <f t="shared" si="22"/>
@@ -10661,7 +10661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="12"/>
-      <c r="F84" s="10"/>
+      <c r="F84" s="12"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
         <f t="shared" si="22"/>
@@ -10730,7 +10730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="12"/>
-      <c r="F85" s="10"/>
+      <c r="F85" s="12"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
         <f t="shared" si="22"/>
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="12"/>
-      <c r="F86" s="10"/>
+      <c r="F86" s="12"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
         <f t="shared" si="22"/>
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="12"/>
-      <c r="F87" s="10"/>
+      <c r="F87" s="12"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
         <f t="shared" si="22"/>
@@ -10937,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="12"/>
-      <c r="F88" s="10"/>
+      <c r="F88" s="12"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
         <f t="shared" si="22"/>
@@ -11006,7 +11006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="12"/>
-      <c r="F89" s="10"/>
+      <c r="F89" s="12"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
         <f t="shared" si="22"/>
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="12"/>
-      <c r="F90" s="10"/>
+      <c r="F90" s="12"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12">
         <f t="shared" si="22"/>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="12"/>
-      <c r="F91" s="10"/>
+      <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
         <f t="shared" si="22"/>
@@ -11213,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11227,7 +11227,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11240,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="12"/>
-      <c r="F93" s="10"/>
+      <c r="F93" s="12"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
         <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
@@ -11296,7 +11296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="12"/>
-      <c r="F94" s="10"/>
+      <c r="F94" s="12"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
         <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
@@ -11365,7 +11365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="12"/>
-      <c r="F95" s="10"/>
+      <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
         <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
@@ -11434,7 +11434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="12"/>
-      <c r="F96" s="10"/>
+      <c r="F96" s="12"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
         <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
@@ -11503,7 +11503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="12"/>
-      <c r="F97" s="10"/>
+      <c r="F97" s="12"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
         <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
@@ -11572,7 +11572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="12"/>
-      <c r="F98" s="10"/>
+      <c r="F98" s="12"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
         <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
@@ -11641,7 +11641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="12"/>
-      <c r="F99" s="10"/>
+      <c r="F99" s="12"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
         <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
@@ -11710,7 +11710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="12"/>
-      <c r="F100" s="10"/>
+      <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
         <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11792,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="12"/>
-      <c r="F101" s="10"/>
+      <c r="F101" s="12"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
         <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
@@ -11848,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11862,7 +11862,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="5"/>
-      <c r="F103" s="1"/>
+      <c r="F103" s="5"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
         <f t="shared" si="22"/>
@@ -11931,7 +11931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="5"/>
-      <c r="F104" s="1"/>
+      <c r="F104" s="5"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
         <f t="shared" si="22"/>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="E105" s="5"/>
-      <c r="F105" s="1"/>
+      <c r="F105" s="5"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
         <f t="shared" si="22"/>
@@ -12069,7 +12069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="5"/>
-      <c r="F106" s="1"/>
+      <c r="F106" s="5"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
         <f t="shared" si="22"/>
@@ -12138,7 +12138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>0</v>
       </c>
       <c r="E107" s="5"/>
-      <c r="F107" s="1"/>
+      <c r="F107" s="5"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5">
         <f t="shared" si="22"/>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="5"/>
-      <c r="F108" s="1"/>
+      <c r="F108" s="5"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5">
         <f t="shared" si="22"/>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="5"/>
-      <c r="F109" s="1"/>
+      <c r="F109" s="5"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5">
         <f t="shared" si="22"/>
@@ -12345,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="5"/>
-      <c r="F110" s="1"/>
+      <c r="F110" s="5"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5">
         <f t="shared" si="22"/>
@@ -12414,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12425,13 +12425,13 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
-      <c r="F112" s="1"/>
+      <c r="F112" s="5"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5">
         <f t="shared" si="22"/>
@@ -12487,13 +12487,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
-      <c r="F113" s="1"/>
+      <c r="F113" s="5"/>
       <c r="G113" s="5"/>
       <c r="H113" s="5">
         <f t="shared" si="22"/>
@@ -12549,13 +12549,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
-      <c r="F114" s="1"/>
+      <c r="F114" s="5"/>
       <c r="G114" s="5"/>
       <c r="H114" s="5">
         <f t="shared" si="22"/>
@@ -12611,13 +12611,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="1"/>
+      <c r="F115" s="5"/>
       <c r="G115" s="5"/>
       <c r="H115" s="5">
         <f t="shared" si="22"/>
@@ -12673,13 +12673,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
-      <c r="F116" s="1"/>
+      <c r="F116" s="5"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5">
         <f t="shared" si="22"/>
@@ -12735,13 +12735,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="1"/>
+      <c r="F117" s="5"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5">
         <f t="shared" si="22"/>
@@ -12797,13 +12797,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="1"/>
+      <c r="F118" s="5"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5">
         <f t="shared" si="22"/>
@@ -12859,13 +12859,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="1"/>
+      <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
         <f t="shared" si="22"/>
@@ -12921,13 +12921,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="1"/>
+      <c r="F120" s="5"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5">
         <f t="shared" si="22"/>
@@ -12983,13 +12983,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
-      <c r="F121" s="1"/>
+      <c r="F121" s="5"/>
       <c r="G121" s="5"/>
       <c r="H121" s="5">
         <f t="shared" si="22"/>
@@ -13045,13 +13045,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="1"/>
+      <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5">
         <f t="shared" si="22"/>
@@ -13107,13 +13107,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
-      <c r="F123" s="1"/>
+      <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5">
         <f t="shared" si="22"/>
@@ -13169,13 +13169,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
-      <c r="F124" s="1"/>
+      <c r="F124" s="5"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5">
         <f t="shared" si="22"/>
@@ -13231,13 +13231,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
-      <c r="F125" s="1"/>
+      <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5">
         <f t="shared" si="22"/>
@@ -13293,13 +13293,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
-      <c r="F126" s="1"/>
+      <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5">
         <f t="shared" si="22"/>
@@ -13355,13 +13355,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="5"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -13414,191 +13414,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="128" spans="1:27" ht="15"/>
+    <row r="129" ht="15"/>
+    <row r="130" ht="15"/>
+    <row r="131" ht="15"/>
+    <row r="132" ht="15"/>
+    <row r="133" ht="15"/>
+    <row r="134" ht="15"/>
+    <row r="135" ht="15"/>
+    <row r="136" ht="15"/>
+    <row r="137" ht="15"/>
+    <row r="138" ht="15"/>
+    <row r="139" ht="15"/>
+    <row r="140" ht="15"/>
+    <row r="141" ht="15"/>
+    <row r="142" ht="15"/>
+    <row r="143" ht="15"/>
+    <row r="144" ht="15"/>
+    <row r="145" ht="15"/>
+    <row r="146" ht="15"/>
+    <row r="147" ht="15"/>
+    <row r="148" ht="15"/>
+    <row r="149" ht="15"/>
+    <row r="150" ht="15"/>
+    <row r="151" ht="15"/>
+    <row r="152" ht="15"/>
+    <row r="153" ht="15"/>
+    <row r="154" ht="15"/>
+    <row r="155" ht="15"/>
+    <row r="156" ht="15"/>
+    <row r="157" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 D63:E71 H63:I71 Q63:R71 W63:X71 D73:E81 H73:I81 Q73:R81 W73:X81 D83:E91 H83:I91 Q83:R91 W83:X91 D93:E101 H93:I101 Q93:R101 W93:X101 D103:E110 H103:I110 Q103:R110 W103:X110 D112:E127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D53:F61 D5:F12" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 F63:G71 F73:G81 F83:G91 F93:G101 F103:G110 F112:G127" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13611,11 +13461,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G73:G81 G83:G91 G93:G101 G63:G71 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+      <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
-      <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F61 F63:F101 F103:F127 L5:L127 R5:R127 X5:X127" xr:uid="{F7826A56-66A0-4D6C-9D9A-157A82A47EC3}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22084,8 +21934,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F122 L3:L122 R3:R122 X3:X122" xr:uid="{DB875409-070A-42B5-91C1-81298AC52A5F}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
